--- a/Project/ManPowerGT/ManPowerGT_Master_TestCase.xlsx
+++ b/Project/ManPowerGT/ManPowerGT_Master_TestCase.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Case (SKN)'!$A$3:$N$98</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Issue SIT'!$A$3:$N$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Issue SIT'!$A$3:$N$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,6 +49,21 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E7D37"/>
     </font>
   </fonts>
   <fills count="4">
@@ -95,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -110,6 +125,19 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -477,10 +505,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -583,14 +611,154 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Tipe / Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Priority High</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Priority Medium</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Priority Low</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Issue SIT (awal)</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Total SKN</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
         <v>95</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Hasil eksekusi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Tanggal uji</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Metode</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Automation SIT Playwright (Live UI MAVEN http://127.0.0.1:5027) + White-box source verification (Views/JS PowerGT Master).</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -604,23 +772,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N98"/>
+  <dimension ref="A1:O98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="44" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="52" customWidth="1" min="8" max="8"/>
     <col width="52" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="56" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -630,10 +799,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
+    <row r="2" ht="48" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Sumber: MAVEN Views/PowerGT/Master/* dan wwwroot/js/powergt/master/*. Filter kolom Modul / Area untuk satu master. Status Uji / Hasil Aktual / Tester / Tanggal Uji diisi saat eksekusi. Sheet Issue SIT: log lama Product+Reason, Ref ID = Scenario ID di sheet ini.</t>
+          <t>Sumber: MAVEN Views/PowerGT/Master/* dan wwwroot/js/powergt/master/*. Hanya modul master. Filter kolom Modul / Area. Kolom Status Uji / Hasil Aktual / QA / Tanggal Uji diisi saat eksekusi. Sheet Issue SIT: baris baru bila SKN Fail; Ref ID = Scenario ID.</t>
         </is>
       </c>
     </row>
@@ -700,7 +869,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -708,8 +877,13 @@
           <t>Tanggal Uji</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="72" customHeight="1">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="150" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>1</v>
       </c>
@@ -767,14 +941,39 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr"/>
-      <c r="M4" s="6" t="inlineStr"/>
-      <c r="N4" s="6" t="inlineStr"/>
-    </row>
-    <row r="5" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Judul halaman: Product.
+2. [Sesuai] Tiga kartu: Total, Active, Inactive. Kartu Total berstatus Filtered.
+3. [Sesuai] Grid kolom: No, Code, Product, Umbrella Brand, Brand, Unit, Selling Price, Tax, Status.
+4. [Sesuai] Tidak ada kolom Action.
+5. [Sesuai] Nama Product berupa tautan hijau tebal.
+6. [Sesuai] Tombol Add Product tampil.
+7. [Sesuai] Tidak ada pindah ke halaman Create/Detail terpisah.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O4" s="11" t="inlineStr">
+        <is>
+          <t>SKN-001.png
+7 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="94" customHeight="1">
       <c r="A5" s="7" t="n">
         <v>2</v>
       </c>
@@ -828,14 +1027,35 @@
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr"/>
-      <c r="M5" s="7" t="inlineStr"/>
-      <c r="N5" s="7" t="inlineStr"/>
-    </row>
-    <row r="6" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Tampil gambar ~/assets/img/data_not_found.png (tinggi sekitar 280px).
+2. [Sesuai] Teks: No data available to show.
+3. [Sesuai] Blok empty mengisi area scroll (min-height sekitar 360px), bukan stub kecil di tengah.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O5" s="11" t="inlineStr">
+        <is>
+          <t>SKN-002.png
+3 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="66" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>3</v>
       </c>
@@ -886,14 +1106,33 @@
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr"/>
-      <c r="M6" s="6" t="inlineStr"/>
-      <c r="N6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Tombol Add Product (hijau, ikon plus) tampil di header list.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O6" s="11" t="inlineStr">
+        <is>
+          <t>SKN-003.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1">
       <c r="A7" s="7" t="n">
         <v>4</v>
       </c>
@@ -946,14 +1185,34 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr"/>
-      <c r="M7" s="7" t="inlineStr"/>
-      <c r="N7" s="7" t="inlineStr"/>
-    </row>
-    <row r="8" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L7" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Tombol Add Product tidak dirender.
+2. [Sesuai] List tetap bisa dilihat. Klik nama Product membuka form View (bukan Add).
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O7" s="11" t="inlineStr">
+        <is>
+          <t>SKN-004.png
+2 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="136" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>5</v>
       </c>
@@ -1012,14 +1271,38 @@
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="inlineStr"/>
-      <c r="M8" s="6" t="inlineStr"/>
-      <c r="N8" s="6" t="inlineStr"/>
-    </row>
-    <row r="9" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Hanya satu kartu yang is-filtered (badge Filtered putih).
+2. [Sesuai] Active: hanya baris badge Active.
+3. [Sesuai] Inactive: hanya baris badge Inactive.
+4. [Sesuai] Total: semua status.
+5. [Sesuai] Input search per kolom dikosongkan saat ganti kartu.
+6. [Sesuai] Hitungan kartu sesuai data (Total / Active / Inactive).
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O8" s="11" t="inlineStr">
+        <is>
+          <t>SKN-005.png
+6 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="108" customHeight="1">
       <c r="A9" s="7" t="n">
         <v>6</v>
       </c>
@@ -1076,14 +1359,36 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L9" s="7" t="inlineStr"/>
-      <c r="M9" s="7" t="inlineStr"/>
-      <c r="N9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Langkah 2: grid tidak berubah (tidak auto-filter keyup).
+2. [Sesuai] Langkah 3: grid terfilter sesuai Code.
+3. [Sesuai] Enter memicu search yang sama.
+4. [Sesuai] Kolom tanpa nilai search tidak ikut memfilter.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O9" s="11" t="inlineStr">
+        <is>
+          <t>SKN-006.png
+4 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="122" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>7</v>
       </c>
@@ -1139,14 +1444,37 @@
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L10" s="6" t="inlineStr"/>
-      <c r="M10" s="6" t="inlineStr"/>
-      <c r="N10" s="6" t="inlineStr"/>
-    </row>
-    <row r="11" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L10" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] List tersembunyi, form detail tampil di halaman yang sama.
+2. [Sesuai] Header ganti: Back + Save Product (Save hanya jika bitEdit).
+3. [Sesuai] Judul form: Edit Product (edit) atau View Product (view-only).
+4. [Sesuai] Field terisi dari GetByGuid: Code, Name, Umbrella Brand, Brand, Category, harga, tax, unit, status, foto.
+5. [Sesuai] Tidak navigasi ke /MasterData/Product/Detail.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O10" s="11" t="inlineStr">
+        <is>
+          <t>SKN-007.png
+5 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="94" customHeight="1">
       <c r="A11" s="7" t="n">
         <v>8</v>
       </c>
@@ -1202,14 +1530,35 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L11" s="7" t="inlineStr"/>
-      <c r="M11" s="7" t="inlineStr"/>
-      <c r="N11" s="7" t="inlineStr"/>
-    </row>
-    <row r="12" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L11" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Dialog: Back to product list?
+2. [Sesuai] Batal: tetap di form.
+3. [Sesuai] Ya: list tampil kembali, DataTable column width menyesuaikan (tidak pecah).
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O11" s="11" t="inlineStr">
+        <is>
+          <t>SKN-008.png
+3 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="178" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>9</v>
       </c>
@@ -1270,14 +1619,43 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L12" s="6" t="inlineStr"/>
-      <c r="M12" s="6" t="inlineStr"/>
-      <c r="N12" s="6" t="inlineStr"/>
-    </row>
-    <row r="13" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L12" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Judul: Add Product.
+2. [Sesuai] Product Code dan Name kosong dan disabled.
+3. [Sesuai] Tombol LOV SKU (search hijau) tampil.
+4. [Sesuai] Umbrella Brand dan Brand kosong, disabled.
+5. [Sesuai] Category: placeholder select.
+6. [Sesuai] Purchase Price kosong.
+7. [Sesuai] Tax Scheme terisi default (PPN11 jika ada).
+8. [Sesuai] Conversion Unit terisi default (PCS jika ada).
+9. [Sesuai] Product Status: switch Active.
+10. [Sesuai] Foto: No photo available + ilustrasi data_not_found.
+11. [Sesuai] Input file foto tampil (JPG, PNG, max 2 MB).
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O12" s="11" t="inlineStr">
+        <is>
+          <t>SKN-009.png
+11 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="122" customHeight="1">
       <c r="A13" s="7" t="n">
         <v>10</v>
       </c>
@@ -1333,14 +1711,37 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr"/>
-      <c r="M13" s="7" t="inlineStr"/>
-      <c r="N13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L13" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Modal judul: Select Product Code (SKU).
+2. [Sesuai] Input placeholder: Search SKU code or name + tombol search hijau.
+3. [Sesuai] Tabel kolom: Code, Name, Action (tombol Select).
+4. [Sesuai] Pager: Show 10/25/100, Previous / Next, teks Page x of y.
+5. [Sesuai] Load awal memanggil SkuApi (boleh langsung ada data atau Search and select a SKU lalu hasil).
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O13" s="11" t="inlineStr">
+        <is>
+          <t>SKN-010.png
+5 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="122" customHeight="1">
       <c r="A14" s="6" t="n">
         <v>11</v>
       </c>
@@ -1399,14 +1800,37 @@
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L14" s="6" t="inlineStr"/>
-      <c r="M14" s="6" t="inlineStr"/>
-      <c r="N14" s="6" t="inlineStr"/>
-    </row>
-    <row r="15" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L14" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Hasil match code atau name (contains/search API).
+2. [Sesuai] Kolom Code / Name / Select terisi.
+3. [Sesuai] Tidak match: No SKU found.
+4. [Sesuai] Gagal API: Failed to load SKU + notifikasi error.
+5. [Sesuai] Search mereset ke page 1.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O14" s="11" t="inlineStr">
+        <is>
+          <t>SKN-011.png
+5 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="108" customHeight="1">
       <c r="A15" s="7" t="n">
         <v>12</v>
       </c>
@@ -1462,14 +1886,36 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L15" s="7" t="inlineStr"/>
-      <c r="M15" s="7" t="inlineStr"/>
-      <c r="N15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L15" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Modal tertutup.
+2. [Sesuai] Product Code = SkuCode, Product Name = SkuName (disabled).
+3. [Sesuai] Brand dan Umbrella Brand terisi dari skuDetail (brandName, umbrandName) jika API mengembalikan.
+4. [Sesuai] Code tidak bisa diketik manual.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O15" s="11" t="inlineStr">
+        <is>
+          <t>SKN-012.png
+4 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="94" customHeight="1">
       <c r="A16" s="6" t="n">
         <v>13</v>
       </c>
@@ -1524,14 +1970,35 @@
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L16" s="6" t="inlineStr"/>
-      <c r="M16" s="6" t="inlineStr"/>
-      <c r="N16" s="6" t="inlineStr"/>
-    </row>
-    <row r="17" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L16" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Tidak ada request Save (atau save dibatalkan di client).
+2. [Sesuai] Pesan: Product category must be selected.
+3. [Sesuai] Data baru tidak muncul di list.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O16" s="11" t="inlineStr">
+        <is>
+          <t>SKN-013.png
+3 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="108" customHeight="1">
       <c r="A17" s="7" t="n">
         <v>14</v>
       </c>
@@ -1586,14 +2053,36 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L17" s="7" t="inlineStr"/>
-      <c r="M17" s="7" t="inlineStr"/>
-      <c r="N17" s="7" t="inlineStr"/>
-    </row>
-    <row r="18" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L17" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Opsi dari ParamApi GetByName name=PRODUCT_CATEGORY_GT.
+2. [Sesuai] Hanya ParamDetail yang IsActive.
+3. [Sesuai] Urutan mengikuti Order.
+4. [Sesuai] Gagal load: notifikasi Failed to load product categories.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O17" s="11" t="inlineStr">
+        <is>
+          <t>SKN-014.png
+4 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="80" customHeight="1">
       <c r="A18" s="6" t="n">
         <v>15</v>
       </c>
@@ -1647,14 +2136,34 @@
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L18" s="6" t="inlineStr"/>
-      <c r="M18" s="6" t="inlineStr"/>
-      <c r="N18" s="6" t="inlineStr"/>
-    </row>
-    <row r="19" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L18" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Pesan: Product code must be selected from Master Data API.
+2. [Sesuai] Tidak tersimpan.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N18" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O18" s="11" t="inlineStr">
+        <is>
+          <t>SKN-015.png
+2 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="94" customHeight="1">
       <c r="A19" s="7" t="n">
         <v>16</v>
       </c>
@@ -1710,14 +2219,35 @@
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L19" s="7" t="inlineStr"/>
-      <c r="M19" s="7" t="inlineStr"/>
-      <c r="N19" s="7" t="inlineStr"/>
-    </row>
-    <row r="20" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L19" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Save ditolak: Purchase price must be greater than 0.
+2. [Sesuai] Field harga hanya menerima digit dan satu pemisah desimal (. atau ,).
+3. [Sesuai] Paste non-angka dibersihkan.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O19" s="11" t="inlineStr">
+        <is>
+          <t>SKN-016.png
+3 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="94" customHeight="1">
       <c r="A20" s="6" t="n">
         <v>17</v>
       </c>
@@ -1772,14 +2302,35 @@
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L20" s="6" t="inlineStr"/>
-      <c r="M20" s="6" t="inlineStr"/>
-      <c r="N20" s="6" t="inlineStr"/>
-    </row>
-    <row r="21" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L20" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Opsi hanya tax bitActive.
+2. [Sesuai] Save tanpa tax: Tax scheme is required.
+3. [Sesuai] Payload save memakai persen (decPajakID), bukan tax id.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O20" s="11" t="inlineStr">
+        <is>
+          <t>SKN-017.png
+3 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="94" customHeight="1">
       <c r="A21" s="7" t="n">
         <v>18</v>
       </c>
@@ -1834,14 +2385,35 @@
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr"/>
-      <c r="M21" s="7" t="inlineStr"/>
-      <c r="N21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L21" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Field Selling Price disabled, hint: = Purchase Price + VAT.
+2. [Sesuai] Nilai = round(beli * (1 + persen/100), 2), tampilan id-ID.
+3. [Sesuai] Grid list menampilkan Rp {harga jual}.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O21" s="11" t="inlineStr">
+        <is>
+          <t>SKN-018.png
+3 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="108" customHeight="1">
       <c r="A22" s="6" t="n">
         <v>19</v>
       </c>
@@ -1897,14 +2469,36 @@
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L22" s="6" t="inlineStr"/>
-      <c r="M22" s="6" t="inlineStr"/>
-      <c r="N22" s="6" t="inlineStr"/>
-    </row>
-    <row r="23" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L22" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Pesan: Photo format must be one of: .jpg, .jpeg, .png.
+2. [Sesuai] Input file dikosongkan. pendingPhotoFile tidak di-set.
+3. [Sesuai] Preview tidak berganti ke file ilegal.
+4. [Sesuai] Save tanpa foto tetap boleh (foto tidak wajib).
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O22" s="11" t="inlineStr">
+        <is>
+          <t>SKN-019.png
+4 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="80" customHeight="1">
       <c r="A23" s="7" t="n">
         <v>20</v>
       </c>
@@ -1956,14 +2550,34 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L23" s="7" t="inlineStr"/>
-      <c r="M23" s="7" t="inlineStr"/>
-      <c r="N23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L23" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Pesan: Photo size must not exceed 2 MB.
+2. [Sesuai] Input dikosongkan. Preview tidak memakai file itu.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O23" s="11" t="inlineStr">
+        <is>
+          <t>SKN-020.png
+2 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="94" customHeight="1">
       <c r="A24" s="6" t="n">
         <v>21</v>
       </c>
@@ -2018,14 +2632,35 @@
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L24" s="6" t="inlineStr"/>
-      <c r="M24" s="6" t="inlineStr"/>
-      <c r="N24" s="6" t="inlineStr"/>
-    </row>
-    <row r="25" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L24" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Preview tampil (max-height 280px).
+2. [Sesuai] Klik membuka modal Product Photo.
+3. [Sesuai] Saat Save, file dikirim sebagai txtPhoto pada FormData.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O24" s="11" t="inlineStr">
+        <is>
+          <t>SKN-021.png
+3 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="108" customHeight="1">
       <c r="A25" s="7" t="n">
         <v>22</v>
       </c>
@@ -2081,14 +2716,36 @@
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L25" s="7" t="inlineStr"/>
-      <c r="M25" s="7" t="inlineStr"/>
-      <c r="N25" s="7" t="inlineStr"/>
-    </row>
-    <row r="26" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L25" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Dialog: Save this product?
+2. [Sesuai] Batal: tidak ada POST.
+3. [Sesuai] Sukses: toast Success! (timer 1.5s), kembali ke list, grid reload, hitungan kartu ter-update.
+4. [Sesuai] Gagal API: pesan error, tetap di form.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O25" s="11" t="inlineStr">
+        <is>
+          <t>SKN-022.png
+4 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="122" customHeight="1">
       <c r="A26" s="6" t="n">
         <v>23</v>
       </c>
@@ -2144,14 +2801,37 @@
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L26" s="6" t="inlineStr"/>
-      <c r="M26" s="6" t="inlineStr"/>
-      <c r="N26" s="6" t="inlineStr"/>
-    </row>
-    <row r="27" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L26" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Judul: Edit Product.
+2. [Sesuai] Tombol LOV SKU disembunyikan.
+3. [Sesuai] Code, Name, Umbrella, Brand tetap disabled.
+4. [Sesuai] Category, Purchase Price, Tax, Status, foto tetap bisa diubah (jika bitEdit).
+5. [Sesuai] Save memakai Update/Save dengan guid yang sama.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M26" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O26" s="11" t="inlineStr">
+        <is>
+          <t>SKN-023.png
+5 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="94" customHeight="1">
       <c r="A27" s="7" t="n">
         <v>24</v>
       </c>
@@ -2206,14 +2886,35 @@
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L27" s="7" t="inlineStr"/>
-      <c r="M27" s="7" t="inlineStr"/>
-      <c r="N27" s="7" t="inlineStr"/>
-    </row>
-    <row r="28" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L27" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Payload memuat txtInsertedBy = clsGlobal.getCurrentLoginName() (bukan GUID kosong).
+2. [Sesuai] Setelah update, kolom Updated By (jika backend mengisi) sesuai user yang mengubah.
+3. [Sesuai] Bukan GUID session yang mentah.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O27" s="11" t="inlineStr">
+        <is>
+          <t>SKN-024.png
+3 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="108" customHeight="1">
       <c r="A28" s="6" t="n">
         <v>25</v>
       </c>
@@ -2268,14 +2969,36 @@
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L28" s="6" t="inlineStr"/>
-      <c r="M28" s="6" t="inlineStr"/>
-      <c r="N28" s="6" t="inlineStr"/>
-    </row>
-    <row r="29" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L28" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Judul: View Product.
+2. [Sesuai] Save Product tersembunyi. LOV SKU tersembunyi. Upload foto tersembunyi.
+3. [Sesuai] Purchase Price readonly. Tax, Category, Status disabled.
+4. [Sesuai] Back tetap ada (dengan konfirmasi).
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M28" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N28" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O28" s="11" t="inlineStr">
+        <is>
+          <t>SKN-025.png
+4 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="122" customHeight="1">
       <c r="A29" s="7" t="n">
         <v>26</v>
       </c>
@@ -2331,14 +3054,37 @@
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L29" s="7" t="inlineStr"/>
-      <c r="M29" s="7" t="inlineStr"/>
-      <c r="N29" s="7" t="inlineStr"/>
-    </row>
-    <row r="30" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L29" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Judul: Reason.
+2. [Sesuai] Kartu: Total, Active, Inactive, Return, Visit, Order. Total Filtered.
+3. [Sesuai] Kolom: No, Reason Name, Description, Type, Status. Tidak ada kolom Action.
+4. [Sesuai] Nama berupa tautan hijau tebal. Type berupa badge berwarna.
+5. [Sesuai] Inactive memakai badge merah (bg-danger). Add Reason tampil.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O29" s="11" t="inlineStr">
+        <is>
+          <t>SKN-026.png
+5 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="66" customHeight="1">
       <c r="A30" s="6" t="n">
         <v>27</v>
       </c>
@@ -2389,14 +3135,33 @@
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L30" s="6" t="inlineStr"/>
-      <c r="M30" s="6" t="inlineStr"/>
-      <c r="N30" s="6" t="inlineStr"/>
-    </row>
-    <row r="31" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L30" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Tampil ~/assets/img/data_not_found.png (tinggi ~280px) dan teks No data available to show. Blok empty mengisi area scroll (~360px).
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N30" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O30" s="11" t="inlineStr">
+        <is>
+          <t>SKN-027.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="66" customHeight="1">
       <c r="A31" s="7" t="n">
         <v>28</v>
       </c>
@@ -2447,14 +3212,33 @@
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L31" s="7" t="inlineStr"/>
-      <c r="M31" s="7" t="inlineStr"/>
-      <c r="N31" s="7" t="inlineStr"/>
-    </row>
-    <row r="32" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L31" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Tombol Add Reason tampil.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O31" s="11" t="inlineStr">
+        <is>
+          <t>SKN-028.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="108" customHeight="1">
       <c r="A32" s="6" t="n">
         <v>29</v>
       </c>
@@ -2508,14 +3292,36 @@
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L32" s="6" t="inlineStr"/>
-      <c r="M32" s="6" t="inlineStr"/>
-      <c r="N32" s="6" t="inlineStr"/>
-    </row>
-    <row r="33" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L32" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Hanya satu kartu Filtered.
+2. [Sesuai] Active: status Active. Inactive: status Inactive. Total: semua.
+3. [Sesuai] Search kolom dan select Type/Status di header dikosongkan saat ganti kartu.
+4. [Sesuai] Hitungan dari GetList: intTotalReason, intTotalAktif, Inactive = Total-Aktif.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M32" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N32" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O32" s="11" t="inlineStr">
+        <is>
+          <t>SKN-029.png
+4 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="122" customHeight="1">
       <c r="A33" s="7" t="n">
         <v>30</v>
       </c>
@@ -2573,14 +3379,37 @@
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L33" s="7" t="inlineStr"/>
-      <c r="M33" s="7" t="inlineStr"/>
-      <c r="N33" s="7" t="inlineStr"/>
-    </row>
-    <row r="34" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L33" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Return: hanya Type Return.
+2. [Sesuai] Visit: filter txtTipe=Kunjungan (bukan string Visit). Badge di grid tetap label Visit.
+3. [Sesuai] Order: Type Order.
+4. [Sesuai] Select filter Type di header tersinkron (nilai Kunjungan saat kartu Visit).
+5. [Sesuai] Hitungan: cntReturn, cntVisit (intTotalKunjungan), cntOrder.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M33" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N33" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O33" s="11" t="inlineStr">
+        <is>
+          <t>SKN-030.png
+5 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="94" customHeight="1">
       <c r="A34" s="6" t="n">
         <v>31</v>
       </c>
@@ -2637,14 +3466,35 @@
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L34" s="6" t="inlineStr"/>
-      <c r="M34" s="6" t="inlineStr"/>
-      <c r="N34" s="6" t="inlineStr"/>
-    </row>
-    <row r="35" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L34" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Name/Description tidak filter on keyup.
+2. [Sesuai] Select Type memfilter txtTipe (nilai DB, bukan label Visit).
+3. [Sesuai] Select Status: true=Active, false=Inactive.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M34" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N34" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O34" s="11" t="inlineStr">
+        <is>
+          <t>SKN-031.png
+3 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="94" customHeight="1">
       <c r="A35" s="7" t="n">
         <v>32</v>
       </c>
@@ -2698,14 +3548,35 @@
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L35" s="7" t="inlineStr"/>
-      <c r="M35" s="7" t="inlineStr"/>
-      <c r="N35" s="7" t="inlineStr"/>
-    </row>
-    <row r="36" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L35" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Return-&gt;Return, Kunjungan-&gt;Visit, Order-&gt;Order. Type lain tampil apa adanya.
+2. [Sesuai] Warna badge dari palet primary/warning/success/info/danger/dark, satu warna per type.
+3. [Sesuai] Nilai yang disimpan/dikirim ke API tetap ParamDetailName (Kunjungan, bukan Visit).
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M35" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N35" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O35" s="11" t="inlineStr">
+        <is>
+          <t>SKN-032.png
+3 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="80" customHeight="1">
       <c r="A36" s="6" t="n">
         <v>33</v>
       </c>
@@ -2757,14 +3628,34 @@
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L36" s="6" t="inlineStr"/>
-      <c r="M36" s="6" t="inlineStr"/>
-      <c r="N36" s="6" t="inlineStr"/>
-    </row>
-    <row r="37" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L36" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] List hilang, form tampil. Back + Save Reason (Save jika edit).
+2. [Sesuai] Judul Edit Reason. Field terisi GetByGuid. Tidak pindah halaman Detail.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M36" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N36" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O36" s="11" t="inlineStr">
+        <is>
+          <t>SKN-033.png
+2 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="94" customHeight="1">
       <c r="A37" s="7" t="n">
         <v>34</v>
       </c>
@@ -2819,14 +3710,35 @@
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L37" s="7" t="inlineStr"/>
-      <c r="M37" s="7" t="inlineStr"/>
-      <c r="N37" s="7" t="inlineStr"/>
-    </row>
-    <row r="38" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L37" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Save sukses: Reason created. Type di list = badge Visit jika DB Kunjungan.
+2. [Sesuai] Form detail harus menampilkan Type yang sama (dropdown terpilih).
+3. [Sesuai] Jika dropdown kosong padahal DB ada txtTipe: Fail (renderForm memakai val(tipe.toLowerCase()) vs option Case-sensitive).
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O37" s="11" t="inlineStr">
+        <is>
+          <t>SKN-034.png
+3 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="94" customHeight="1">
       <c r="A38" s="6" t="n">
         <v>35</v>
       </c>
@@ -2881,14 +3793,35 @@
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L38" s="6" t="inlineStr"/>
-      <c r="M38" s="6" t="inlineStr"/>
-      <c r="N38" s="6" t="inlineStr"/>
-    </row>
-    <row r="39" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L38" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Tidak ada error tidak enable input data dengan Tipe Reason Visit/Others.
+2. [Sesuai] Data tersimpan. Type di list sesuai mapping label.
+3. [Sesuai] Hanya opsi IsActive dari REASON_CATEGORY_GT yang muncul.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M38" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N38" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O38" s="11" t="inlineStr">
+        <is>
+          <t>SKN-035.png
+3 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="66" customHeight="1">
       <c r="A39" s="7" t="n">
         <v>36</v>
       </c>
@@ -2939,14 +3872,33 @@
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L39" s="7" t="inlineStr"/>
-      <c r="M39" s="7" t="inlineStr"/>
-      <c r="N39" s="7" t="inlineStr"/>
-    </row>
-    <row r="40" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L39" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Pesan: Reason Name is required. Tidak tersimpan.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M39" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N39" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O39" s="11" t="inlineStr">
+        <is>
+          <t>SKN-036.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="66" customHeight="1">
       <c r="A40" s="6" t="n">
         <v>37</v>
       </c>
@@ -2997,14 +3949,33 @@
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L40" s="6" t="inlineStr"/>
-      <c r="M40" s="6" t="inlineStr"/>
-      <c r="N40" s="6" t="inlineStr"/>
-    </row>
-    <row r="41" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L40" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Pesan: Type is required. Tidak tersimpan.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M40" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N40" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O40" s="11" t="inlineStr">
+        <is>
+          <t>SKN-037.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="94" customHeight="1">
       <c r="A41" s="7" t="n">
         <v>38</v>
       </c>
@@ -3058,14 +4029,35 @@
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L41" s="7" t="inlineStr"/>
-      <c r="M41" s="7" t="inlineStr"/>
-      <c r="N41" s="7" t="inlineStr"/>
-    </row>
-    <row r="42" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L41" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Dialog: Save this reason?
+2. [Sesuai] Create: Reason created. Edit: Reason updated.
+3. [Sesuai] Kembali ke list, grid reload.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M41" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N41" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O41" s="11" t="inlineStr">
+        <is>
+          <t>SKN-038.png
+3 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="66" customHeight="1">
       <c r="A42" s="6" t="n">
         <v>39</v>
       </c>
@@ -3116,14 +4108,33 @@
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L42" s="6" t="inlineStr"/>
-      <c r="M42" s="6" t="inlineStr"/>
-      <c r="N42" s="6" t="inlineStr"/>
-    </row>
-    <row r="43" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L42" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Dialog: Back to reason list? Batal tetap di form. Ya kembali list.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M42" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N42" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O42" s="11" t="inlineStr">
+        <is>
+          <t>SKN-039.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="66" customHeight="1">
       <c r="A43" s="7" t="n">
         <v>40</v>
       </c>
@@ -3174,14 +4185,33 @@
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L43" s="7" t="inlineStr"/>
-      <c r="M43" s="7" t="inlineStr"/>
-      <c r="N43" s="7" t="inlineStr"/>
-    </row>
-    <row r="44" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L43" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] btnDeleteReason class d-none, tidak ter-bind. Tidak ada endpoint Delete.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M43" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N43" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O43" s="11" t="inlineStr">
+        <is>
+          <t>SKN-040.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="80" customHeight="1">
       <c r="A44" s="6" t="n">
         <v>41</v>
       </c>
@@ -3235,14 +4265,34 @@
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L44" s="6" t="inlineStr"/>
-      <c r="M44" s="6" t="inlineStr"/>
-      <c r="N44" s="6" t="inlineStr"/>
-    </row>
-    <row r="45" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L44" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Kolom terisi nama/user login, bukan GUID mentah.
+2. [Sesuai] Jika kosong/GUID: Fail (backend).
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M44" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N44" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O44" s="11" t="inlineStr">
+        <is>
+          <t>SKN-041.png
+2 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="122" customHeight="1">
       <c r="A45" s="7" t="n">
         <v>42</v>
       </c>
@@ -3298,14 +4348,37 @@
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L45" s="7" t="inlineStr"/>
-      <c r="M45" s="7" t="inlineStr"/>
-      <c r="N45" s="7" t="inlineStr"/>
-    </row>
-    <row r="46" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L45" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Judul Channel. Badge View-only.
+2. [Sesuai] Tidak ada Add / Save / Back detail.
+3. [Sesuai] Kolom: No, Channel, Type Customer, Account.
+4. [Sesuai] Filter: tiga select (bukan input+tombol search).
+5. [Sesuai] Klik baris tidak membuka detail.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N45" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O45" s="11" t="inlineStr">
+        <is>
+          <t>SKN-042.png
+5 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="94" customHeight="1">
       <c r="A46" s="6" t="n">
         <v>43</v>
       </c>
@@ -3358,14 +4431,35 @@
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L46" s="6" t="inlineStr"/>
-      <c r="M46" s="6" t="inlineStr"/>
-      <c r="N46" s="6" t="inlineStr"/>
-    </row>
-    <row r="47" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L46" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Channel = OutletChannelTypeName dari account type.
+2. [Sesuai] Type Customer = TypePartnerName. Account = OutletAccountTypeName.
+3. [Sesuai] Hanya TypePartner IsActive. Gagal API: Failed to load Channel list, grid kosong.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M46" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N46" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O46" s="11" t="inlineStr">
+        <is>
+          <t>SKN-043.png
+3 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="80" customHeight="1">
       <c r="A47" s="7" t="n">
         <v>44</v>
       </c>
@@ -3419,14 +4513,34 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L47" s="7" t="inlineStr"/>
-      <c r="M47" s="7" t="inlineStr"/>
-      <c r="N47" s="7" t="inlineStr"/>
-    </row>
-    <row r="48" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L47" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Filter exact (regex ^nilai$). Kombinasi AND antar kolom.
+2. [Sesuai] Opsi select terisi unik dari data, terurut.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M47" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N47" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O47" s="11" t="inlineStr">
+        <is>
+          <t>SKN-044.png
+2 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="66" customHeight="1">
       <c r="A48" s="6" t="n">
         <v>45</v>
       </c>
@@ -3477,14 +4591,33 @@
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L48" s="6" t="inlineStr"/>
-      <c r="M48" s="6" t="inlineStr"/>
-      <c r="N48" s="6" t="inlineStr"/>
-    </row>
-    <row r="49" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L48" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Gambar data_not_found.png. Teks: no data available in table (huruf kecil, beda dari master lain).
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M48" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N48" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O48" s="11" t="inlineStr">
+        <is>
+          <t>SKN-045.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="94" customHeight="1">
       <c r="A49" s="7" t="n">
         <v>46</v>
       </c>
@@ -3537,14 +4670,35 @@
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L49" s="7" t="inlineStr"/>
-      <c r="M49" s="7" t="inlineStr"/>
-      <c r="N49" s="7" t="inlineStr"/>
-    </row>
-    <row r="50" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L49" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Kartu: Total, Active, Inactive, With GPS. Total Filtered.
+2. [Sesuai] Kolom: No, Code, Name, City, Channel, Salesman, Status.
+3. [Sesuai] Name tautan hijau. Tidak ada tombol Add.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M49" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N49" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O49" s="11" t="inlineStr">
+        <is>
+          <t>SKN-046.png
+3 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="66" customHeight="1">
       <c r="A50" s="6" t="n">
         <v>47</v>
       </c>
@@ -3595,14 +4749,33 @@
       </c>
       <c r="K50" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L50" s="6" t="inlineStr"/>
-      <c r="M50" s="6" t="inlineStr"/>
-      <c r="N50" s="6" t="inlineStr"/>
-    </row>
-    <row r="51" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L50" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Hanya baris dengan GPS. Kartu With GPS Filtered. Search kolom ter-reset.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M50" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N50" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O50" s="11" t="inlineStr">
+        <is>
+          <t>SKN-047.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="66" customHeight="1">
       <c r="A51" s="7" t="n">
         <v>48</v>
       </c>
@@ -3655,14 +4828,33 @@
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L51" s="7" t="inlineStr"/>
-      <c r="M51" s="7" t="inlineStr"/>
-      <c r="N51" s="7" t="inlineStr"/>
-    </row>
-    <row r="52" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L51" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Grid terfilter setelah klik/Enter saja.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M51" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N51" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O51" s="11" t="inlineStr">
+        <is>
+          <t>SKN-048.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="108" customHeight="1">
       <c r="A52" s="6" t="n">
         <v>49</v>
       </c>
@@ -3716,14 +4908,36 @@
       </c>
       <c r="K52" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L52" s="6" t="inlineStr"/>
-      <c r="M52" s="6" t="inlineStr"/>
-      <c r="N52" s="6" t="inlineStr"/>
-    </row>
-    <row r="53" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L52" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] List hilang. Header Back saja (tidak ada Save).
+2. [Sesuai] Profil: nama, kode, status, channel.
+3. [Sesuai] Section: Store &amp; Contact, Address, Location Map, Store Photo.
+4. [Sesuai] Semua input disabled. GetByGuid mengisi sisa field.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M52" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N52" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O52" s="11" t="inlineStr">
+        <is>
+          <t>SKN-049.png
+4 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="80" customHeight="1">
       <c r="A53" s="7" t="n">
         <v>50</v>
       </c>
@@ -3776,14 +4990,34 @@
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L53" s="7" t="inlineStr"/>
-      <c r="M53" s="7" t="inlineStr"/>
-      <c r="N53" s="7" t="inlineStr"/>
-    </row>
-    <row r="54" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L53" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Valid: GPS lat, lng. Tombol Google Maps href maps?q=lat,lng. Marker Leaflet.
+2. [Sesuai] Invalid (kosong, NaN, 0,0, di luar range): GPS —, tombol Maps hidden, teks No valid coordinates to show on the map.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M53" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N53" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O53" s="11" t="inlineStr">
+        <is>
+          <t>SKN-050.png
+2 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="66" customHeight="1">
       <c r="A54" s="6" t="n">
         <v>51</v>
       </c>
@@ -3834,14 +5068,33 @@
       </c>
       <c r="K54" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L54" s="6" t="inlineStr"/>
-      <c r="M54" s="6" t="inlineStr"/>
-      <c r="N54" s="6" t="inlineStr"/>
-    </row>
-    <row r="55" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L54" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Modal Store Photo menampilkan gambar. Tanpa foto: placeholder, klik tidak wajib buka modal.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M54" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N54" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O54" s="11" t="inlineStr">
+        <is>
+          <t>SKN-051.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="66" customHeight="1">
       <c r="A55" s="7" t="n">
         <v>52</v>
       </c>
@@ -3892,14 +5145,33 @@
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L55" s="7" t="inlineStr"/>
-      <c r="M55" s="7" t="inlineStr"/>
-      <c r="N55" s="7" t="inlineStr"/>
-    </row>
-    <row r="56" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L55" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Dialog: Back to customer list?
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M55" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N55" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O55" s="11" t="inlineStr">
+        <is>
+          <t>SKN-052.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="66" customHeight="1">
       <c r="A56" s="6" t="n">
         <v>53</v>
       </c>
@@ -3950,14 +5222,33 @@
       </c>
       <c r="K56" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L56" s="6" t="inlineStr"/>
-      <c r="M56" s="6" t="inlineStr"/>
-      <c r="N56" s="6" t="inlineStr"/>
-    </row>
-    <row r="57" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L56" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Tampil ~/assets/img/data_not_found.png (tinggi ~280px) dan teks No data available to show. Blok empty mengisi area scroll (~360px).
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M56" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N56" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O56" s="11" t="inlineStr">
+        <is>
+          <t>SKN-053.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="94" customHeight="1">
       <c r="A57" s="7" t="n">
         <v>54</v>
       </c>
@@ -4010,14 +5301,35 @@
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L57" s="7" t="inlineStr"/>
-      <c r="M57" s="7" t="inlineStr"/>
-      <c r="N57" s="7" t="inlineStr"/>
-    </row>
-    <row r="58" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L57" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Judul Employee. Kartu Total Filtered, Motoris, SPG GT, Active.
+2. [Sesuai] Kolom: No, NIK, Name, Role, Branch, Region, Status. Name tautan hijau.
+3. [Sesuai] Download Data tampil. Upload Data + Edit tampil (bitEdit).
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M57" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N57" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O57" s="11" t="inlineStr">
+        <is>
+          <t>SKN-054.png
+3 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="80" customHeight="1">
       <c r="A58" s="6" t="n">
         <v>55</v>
       </c>
@@ -4069,14 +5381,34 @@
       </c>
       <c r="K58" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L58" s="6" t="inlineStr"/>
-      <c r="M58" s="6" t="inlineStr"/>
-      <c r="N58" s="6" t="inlineStr"/>
-    </row>
-    <row r="59" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L58" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Motoris: cardFilter motoris. SPG GT: spg gt. Active: active.
+2. [Sesuai] Hitungan: intTotalPegawai, intTotalMotoris, intTotalSpgGt, intTotalAktif.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M58" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N58" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O58" s="11" t="inlineStr">
+        <is>
+          <t>SKN-055.png
+2 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="66" customHeight="1">
       <c r="A59" s="7" t="n">
         <v>56</v>
       </c>
@@ -4129,14 +5461,33 @@
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L59" s="7" t="inlineStr"/>
-      <c r="M59" s="7" t="inlineStr"/>
-      <c r="N59" s="7" t="inlineStr"/>
-    </row>
-    <row r="60" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L59" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Tidak auto-filter keyup.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M59" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N59" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O59" s="11" t="inlineStr">
+        <is>
+          <t>SKN-056.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="94" customHeight="1">
       <c r="A60" s="6" t="n">
         <v>57</v>
       </c>
@@ -4189,14 +5540,35 @@
       </c>
       <c r="K60" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L60" s="6" t="inlineStr"/>
-      <c r="M60" s="6" t="inlineStr"/>
-      <c r="N60" s="6" t="inlineStr"/>
-    </row>
-    <row r="61" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L60" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Header Back. Profile: NIK, Name, Role, Phone, Status (disabled).
+2. [Sesuai] Assignment: Branch, Region, Notes.
+3. [Sesuai] Status history terisi GetByGuid. Tidak ada Save.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M60" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N60" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O60" s="11" t="inlineStr">
+        <is>
+          <t>SKN-057.png
+3 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="66" customHeight="1">
       <c r="A61" s="7" t="n">
         <v>58</v>
       </c>
@@ -4247,14 +5619,33 @@
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L61" s="7" t="inlineStr"/>
-      <c r="M61" s="7" t="inlineStr"/>
-      <c r="N61" s="7" t="inlineStr"/>
-    </row>
-    <row r="62" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L61" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Request GtEmployee/ExportExcel. File terunduh / tidak 403 untuk user berhak.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M61" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N61" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O61" s="11" t="inlineStr">
+        <is>
+          <t>SKN-058.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="80" customHeight="1">
       <c r="A62" s="6" t="n">
         <v>59</v>
       </c>
@@ -4306,14 +5697,34 @@
       </c>
       <c r="K62" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L62" s="6" t="inlineStr"/>
-      <c r="M62" s="6" t="inlineStr"/>
-      <c r="N62" s="6" t="inlineStr"/>
-    </row>
-    <row r="63" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L62" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] accept=.csv. Sukses: Upload successful, grid+summary reload. Input file dikosongkan.
+2. [Sesuai] Gagal: swal error, input dikosongkan.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M62" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N62" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O62" s="11" t="inlineStr">
+        <is>
+          <t>SKN-059.png
+2 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="80" customHeight="1">
       <c r="A63" s="7" t="n">
         <v>60</v>
       </c>
@@ -4365,14 +5776,34 @@
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L63" s="7" t="inlineStr"/>
-      <c r="M63" s="7" t="inlineStr"/>
-      <c r="N63" s="7" t="inlineStr"/>
-    </row>
-    <row r="64" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L63" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Modal Edit. Kolom: NIK, Name, Role, Branch, Region, Phone, Notes, Status.
+2. [Sesuai] Save memanggil Upload. Grid list reload.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M63" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N63" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O63" s="11" t="inlineStr">
+        <is>
+          <t>SKN-060.png
+2 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="66" customHeight="1">
       <c r="A64" s="6" t="n">
         <v>61</v>
       </c>
@@ -4423,14 +5854,33 @@
       </c>
       <c r="K64" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L64" s="6" t="inlineStr"/>
-      <c r="M64" s="6" t="inlineStr"/>
-      <c r="N64" s="6" t="inlineStr"/>
-    </row>
-    <row r="65" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L64" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Upload Data dan Edit tidak dirender. Download Data boleh tetap ada.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M64" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N64" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O64" s="11" t="inlineStr">
+        <is>
+          <t>SKN-061.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="66" customHeight="1">
       <c r="A65" s="7" t="n">
         <v>62</v>
       </c>
@@ -4481,14 +5931,33 @@
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L65" s="7" t="inlineStr"/>
-      <c r="M65" s="7" t="inlineStr"/>
-      <c r="N65" s="7" t="inlineStr"/>
-    </row>
-    <row r="66" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L65" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Dialog: Back to employee list?
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M65" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N65" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O65" s="11" t="inlineStr">
+        <is>
+          <t>SKN-062.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="66" customHeight="1">
       <c r="A66" s="6" t="n">
         <v>63</v>
       </c>
@@ -4539,14 +6008,33 @@
       </c>
       <c r="K66" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L66" s="6" t="inlineStr"/>
-      <c r="M66" s="6" t="inlineStr"/>
-      <c r="N66" s="6" t="inlineStr"/>
-    </row>
-    <row r="67" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L66" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Tampil ~/assets/img/data_not_found.png (tinggi ~280px) dan teks No data available to show. Blok empty mengisi area scroll (~360px).
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M66" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N66" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O66" s="11" t="inlineStr">
+        <is>
+          <t>SKN-063.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="94" customHeight="1">
       <c r="A67" s="7" t="n">
         <v>64</v>
       </c>
@@ -4599,14 +6087,35 @@
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L67" s="7" t="inlineStr"/>
-      <c r="M67" s="7" t="inlineStr"/>
-      <c r="N67" s="7" t="inlineStr"/>
-    </row>
-    <row r="68" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L67" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Kartu Total, Active, Inactive, With GPS.
+2. [Sesuai] Kolom: Outlet ID, Name, Branch, Region, Status (plus No). Name tautan hijau.
+3. [Sesuai] Download Data. Upload+Edit jika bitEdit.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M67" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N67" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O67" s="11" t="inlineStr">
+        <is>
+          <t>SKN-064.png
+3 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="66" customHeight="1">
       <c r="A68" s="6" t="n">
         <v>65</v>
       </c>
@@ -4657,14 +6166,33 @@
       </c>
       <c r="K68" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L68" s="6" t="inlineStr"/>
-      <c r="M68" s="6" t="inlineStr"/>
-      <c r="N68" s="6" t="inlineStr"/>
-    </row>
-    <row r="69" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L68" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Hanya row dengan GPS. cardFilter=gps.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M68" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N68" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O68" s="11" t="inlineStr">
+        <is>
+          <t>SKN-065.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="66" customHeight="1">
       <c r="A69" s="7" t="n">
         <v>66</v>
       </c>
@@ -4717,14 +6245,33 @@
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L69" s="7" t="inlineStr"/>
-      <c r="M69" s="7" t="inlineStr"/>
-      <c r="N69" s="7" t="inlineStr"/>
-    </row>
-    <row r="70" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L69" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Tidak auto-filter keyup.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M69" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N69" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O69" s="11" t="inlineStr">
+        <is>
+          <t>SKN-066.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="122" customHeight="1">
       <c r="A70" s="6" t="n">
         <v>67</v>
       </c>
@@ -4779,14 +6326,37 @@
       </c>
       <c r="K70" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L70" s="6" t="inlineStr"/>
-      <c r="M70" s="6" t="inlineStr"/>
-      <c r="N70" s="6" t="inlineStr"/>
-    </row>
-    <row r="71" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L70" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Header Back. Profile: Outlet ID, Name, Phone, Status.
+2. [Sesuai] Location: Branch, Region, Address, City, GPS.
+3. [Sesuai] Map, Stock Summary (Total SKU, Qty Carton, Last Updated),
+4. [Sesuai] Stock by Product, Stock Input History, Status History.
+5. [Sesuai] GetByGuid mengisi nested. Semua field disabled.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M70" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N70" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O70" s="11" t="inlineStr">
+        <is>
+          <t>SKN-067.png
+5 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="80" customHeight="1">
       <c r="A71" s="7" t="n">
         <v>68</v>
       </c>
@@ -4838,14 +6408,34 @@
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L71" s="7" t="inlineStr"/>
-      <c r="M71" s="7" t="inlineStr"/>
-      <c r="N71" s="7" t="inlineStr"/>
-    </row>
-    <row r="72" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L71" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Valid: lat, lng, tombol Maps, marker.
+2. [Sesuai] Invalid: GPS —, Maps hidden, No valid coordinates to show on the map.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M71" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N71" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O71" s="11" t="inlineStr">
+        <is>
+          <t>SKN-068.png
+2 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="80" customHeight="1">
       <c r="A72" s="6" t="n">
         <v>69</v>
       </c>
@@ -4897,14 +6487,34 @@
       </c>
       <c r="K72" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L72" s="6" t="inlineStr"/>
-      <c r="M72" s="6" t="inlineStr"/>
-      <c r="N72" s="6" t="inlineStr"/>
-    </row>
-    <row r="73" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L72" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Ada data: Code, Product, Qty terisi. History punya Date/Motoris/Notes.
+2. [Sesuai] Kosong: empty state data_not_found + No data available to show.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M72" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N72" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O72" s="11" t="inlineStr">
+        <is>
+          <t>SKN-069.png
+2 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="66" customHeight="1">
       <c r="A73" s="7" t="n">
         <v>70</v>
       </c>
@@ -4955,14 +6565,33 @@
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L73" s="7" t="inlineStr"/>
-      <c r="M73" s="7" t="inlineStr"/>
-      <c r="N73" s="7" t="inlineStr"/>
-    </row>
-    <row r="74" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L73" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Request GtStockist/ExportExcel.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M73" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N73" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O73" s="11" t="inlineStr">
+        <is>
+          <t>SKN-070.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="80" customHeight="1">
       <c r="A74" s="6" t="n">
         <v>71</v>
       </c>
@@ -5014,14 +6643,34 @@
       </c>
       <c r="K74" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L74" s="6" t="inlineStr"/>
-      <c r="M74" s="6" t="inlineStr"/>
-      <c r="N74" s="6" t="inlineStr"/>
-    </row>
-    <row r="75" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L74" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Sukses: Upload successful, reload.
+2. [Sesuai] Gagal: pesan + hingga 5 baris errors. Input dikosongkan. accept=.csv.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M74" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N74" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O74" s="11" t="inlineStr">
+        <is>
+          <t>SKN-071.png
+2 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="80" customHeight="1">
       <c r="A75" s="7" t="n">
         <v>72</v>
       </c>
@@ -5073,14 +6722,34 @@
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L75" s="7" t="inlineStr"/>
-      <c r="M75" s="7" t="inlineStr"/>
-      <c r="N75" s="7" t="inlineStr"/>
-    </row>
-    <row r="76" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L75" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Kolom: Outlet ID, Name, Branch, Region, Phone, Address, Latitude, Longitude, Status.
+2. [Sesuai] File upload: stokis_edit.csv. List reload.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M75" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N75" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O75" s="11" t="inlineStr">
+        <is>
+          <t>SKN-072.png
+2 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="66" customHeight="1">
       <c r="A76" s="6" t="n">
         <v>73</v>
       </c>
@@ -5131,14 +6800,33 @@
       </c>
       <c r="K76" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L76" s="6" t="inlineStr"/>
-      <c r="M76" s="6" t="inlineStr"/>
-      <c r="N76" s="6" t="inlineStr"/>
-    </row>
-    <row r="77" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L76" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Dialog: Back to stokis list?
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M76" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N76" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O76" s="11" t="inlineStr">
+        <is>
+          <t>SKN-073.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="66" customHeight="1">
       <c r="A77" s="7" t="n">
         <v>74</v>
       </c>
@@ -5189,14 +6877,33 @@
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L77" s="7" t="inlineStr"/>
-      <c r="M77" s="7" t="inlineStr"/>
-      <c r="N77" s="7" t="inlineStr"/>
-    </row>
-    <row r="78" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L77" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Tampil ~/assets/img/data_not_found.png (tinggi ~280px) dan teks No data available to show. Blok empty mengisi area scroll (~360px).
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M77" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N77" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O77" s="11" t="inlineStr">
+        <is>
+          <t>SKN-074.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="94" customHeight="1">
       <c r="A78" s="6" t="n">
         <v>75</v>
       </c>
@@ -5249,14 +6956,35 @@
       </c>
       <c r="K78" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L78" s="6" t="inlineStr"/>
-      <c r="M78" s="6" t="inlineStr"/>
-      <c r="N78" s="6" t="inlineStr"/>
-    </row>
-    <row r="79" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L78" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Kartu Total/Active/Inactive.
+2. [Sesuai] Kolom: No, Type (badge PPN), Tax Code (tautan hijau), Tax Name, Percentage (%), DPP Value, Status.
+3. [Sesuai] btnAddTax di-hide di init meski Razor merender untuk user edit. Tidak ada create.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M78" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N78" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O78" s="11" t="inlineStr">
+        <is>
+          <t>SKN-075.png
+3 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="66" customHeight="1">
       <c r="A79" s="7" t="n">
         <v>76</v>
       </c>
@@ -5307,14 +7035,33 @@
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L79" s="7" t="inlineStr"/>
-      <c r="M79" s="7" t="inlineStr"/>
-      <c r="N79" s="7" t="inlineStr"/>
-    </row>
-    <row r="80" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L79" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Filter cache GetRatePpn. Satu kartu Filtered. Search kolom ter-reset.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M79" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N79" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O79" s="11" t="inlineStr">
+        <is>
+          <t>SKN-076.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="66" customHeight="1">
       <c r="A80" s="6" t="n">
         <v>77</v>
       </c>
@@ -5367,14 +7114,33 @@
       </c>
       <c r="K80" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L80" s="6" t="inlineStr"/>
-      <c r="M80" s="6" t="inlineStr"/>
-      <c r="N80" s="6" t="inlineStr"/>
-    </row>
-    <row r="81" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L80" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Tidak keyup. Termasuk search Status.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M80" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N80" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O80" s="11" t="inlineStr">
+        <is>
+          <t>SKN-077.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="94" customHeight="1">
       <c r="A81" s="7" t="n">
         <v>78</v>
       </c>
@@ -5427,14 +7193,35 @@
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L81" s="7" t="inlineStr"/>
-      <c r="M81" s="7" t="inlineStr"/>
-      <c r="N81" s="7" t="inlineStr"/>
-    </row>
-    <row r="82" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L81" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Judul View Tax. Type, Code, Name, Percentage, DPP, Effective From/To, Status: disabled.
+2. [Sesuai] Tanggal format DD Mon YYYY (formatDisplayDate).
+3. [Sesuai] btnSaveTax dan btnDeleteTax d-none. Hanya Back.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M81" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N81" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O81" s="11" t="inlineStr">
+        <is>
+          <t>SKN-078.png
+3 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="66" customHeight="1">
       <c r="A82" s="6" t="n">
         <v>79</v>
       </c>
@@ -5485,14 +7272,33 @@
       </c>
       <c r="K82" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L82" s="6" t="inlineStr"/>
-      <c r="M82" s="6" t="inlineStr"/>
-      <c r="N82" s="6" t="inlineStr"/>
-    </row>
-    <row r="83" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L82" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Dialog: Back to tax list?
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M82" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N82" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O82" s="11" t="inlineStr">
+        <is>
+          <t>SKN-079.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="66" customHeight="1">
       <c r="A83" s="7" t="n">
         <v>80</v>
       </c>
@@ -5543,14 +7349,33 @@
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L83" s="7" t="inlineStr"/>
-      <c r="M83" s="7" t="inlineStr"/>
-      <c r="N83" s="7" t="inlineStr"/>
-    </row>
-    <row r="84" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L83" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Failed to load tax rates. Kartu 0. Empty state di grid.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M83" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N83" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O83" s="11" t="inlineStr">
+        <is>
+          <t>SKN-080.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="66" customHeight="1">
       <c r="A84" s="6" t="n">
         <v>81</v>
       </c>
@@ -5601,14 +7426,33 @@
       </c>
       <c r="K84" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L84" s="6" t="inlineStr"/>
-      <c r="M84" s="6" t="inlineStr"/>
-      <c r="N84" s="6" t="inlineStr"/>
-    </row>
-    <row r="85" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L84" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Tampil ~/assets/img/data_not_found.png (tinggi ~280px) dan teks No data available to show. Blok empty mengisi area scroll (~360px).
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M84" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N84" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O84" s="11" t="inlineStr">
+        <is>
+          <t>SKN-081.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="94" customHeight="1">
       <c r="A85" s="7" t="n">
         <v>82</v>
       </c>
@@ -5661,14 +7505,35 @@
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L85" s="7" t="inlineStr"/>
-      <c r="M85" s="7" t="inlineStr"/>
-      <c r="N85" s="7" t="inlineStr"/>
-    </row>
-    <row r="86" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L85" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Kartu Total/Active/Inactive.
+2. [Sesuai] Kolom: No, Limit Name (tautan hijau), Jabatan, Daily Min, Daily Max, Status.
+3. [Sesuai] Add Limit tampil untuk edit.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M85" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N85" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O85" s="11" t="inlineStr">
+        <is>
+          <t>SKN-082.png
+3 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="66" customHeight="1">
       <c r="A86" s="6" t="n">
         <v>83</v>
       </c>
@@ -5719,14 +7584,33 @@
       </c>
       <c r="K86" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L86" s="6" t="inlineStr"/>
-      <c r="M86" s="6" t="inlineStr"/>
-      <c r="N86" s="6" t="inlineStr"/>
-    </row>
-    <row r="87" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L86" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Satu kartu Filtered. Search kolom ter-reset.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M86" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N86" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O86" s="11" t="inlineStr">
+        <is>
+          <t>SKN-083.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="66" customHeight="1">
       <c r="A87" s="7" t="n">
         <v>84</v>
       </c>
@@ -5779,14 +7663,33 @@
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L87" s="7" t="inlineStr"/>
-      <c r="M87" s="7" t="inlineStr"/>
-      <c r="N87" s="7" t="inlineStr"/>
-    </row>
-    <row r="88" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L87" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Tidak keyup.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M87" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N87" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O87" s="11" t="inlineStr">
+        <is>
+          <t>SKN-084.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="122" customHeight="1">
       <c r="A88" s="6" t="n">
         <v>85</v>
       </c>
@@ -5841,14 +7744,37 @@
       </c>
       <c r="K88" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L88" s="6" t="inlineStr"/>
-      <c r="M88" s="6" t="inlineStr"/>
-      <c r="N88" s="6" t="inlineStr"/>
-    </row>
-    <row r="89" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L88" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Judul Add Limit. Limit Name kosong. Jabatan Select Jabatan...
+2. [Sesuai] Type Jabatan tergantung Jabatan. Status Active.
+3. [Sesuai] Daily Min/Max, Weekly/Monthly HKE kosong. End Date Ongoing disabled.
+4. [Sesuai] Start Date min hari ini, nilai awal kosong. Version history tersembunyi.
+5. [Sesuai] Jabatan dari PositionApi GetAllByAppCode.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M88" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N88" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O88" s="11" t="inlineStr">
+        <is>
+          <t>SKN-085.png
+5 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="66" customHeight="1">
       <c r="A89" s="7" t="n">
         <v>86</v>
       </c>
@@ -5900,14 +7826,33 @@
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L89" s="7" t="inlineStr"/>
-      <c r="M89" s="7" t="inlineStr"/>
-      <c r="N89" s="7" t="inlineStr"/>
-    </row>
-    <row r="90" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L89" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Type Jabatan di-reset lalu diisi type milik jabatan terpilih. Gagal API: Failed to load Jabatan list.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M89" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N89" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O89" s="11" t="inlineStr">
+        <is>
+          <t>SKN-086.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="66" customHeight="1">
       <c r="A90" s="6" t="n">
         <v>87</v>
       </c>
@@ -5958,14 +7903,33 @@
       </c>
       <c r="K90" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L90" s="6" t="inlineStr"/>
-      <c r="M90" s="6" t="inlineStr"/>
-      <c r="N90" s="6" t="inlineStr"/>
-    </row>
-    <row r="91" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L90" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Pesan: Limit Name is required.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M90" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N90" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O90" s="11" t="inlineStr">
+        <is>
+          <t>SKN-087.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="66" customHeight="1">
       <c r="A91" s="7" t="n">
         <v>88</v>
       </c>
@@ -6016,14 +7980,33 @@
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L91" s="7" t="inlineStr"/>
-      <c r="M91" s="7" t="inlineStr"/>
-      <c r="N91" s="7" t="inlineStr"/>
-    </row>
-    <row r="92" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L91" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Pesan: Jabatan is required.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M91" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N91" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O91" s="11" t="inlineStr">
+        <is>
+          <t>SKN-088.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="66" customHeight="1">
       <c r="A92" s="6" t="n">
         <v>89</v>
       </c>
@@ -6074,14 +8057,33 @@
       </c>
       <c r="K92" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L92" s="6" t="inlineStr"/>
-      <c r="M92" s="6" t="inlineStr"/>
-      <c r="N92" s="6" t="inlineStr"/>
-    </row>
-    <row r="93" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L92" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Pesan: Daily Min cannot be greater than Daily Max. Field angka (isNumberKey).
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M92" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N92" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O92" s="11" t="inlineStr">
+        <is>
+          <t>SKN-089.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="80" customHeight="1">
       <c r="A93" s="7" t="n">
         <v>90</v>
       </c>
@@ -6133,14 +8135,34 @@
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L93" s="7" t="inlineStr"/>
-      <c r="M93" s="7" t="inlineStr"/>
-      <c r="N93" s="7" t="inlineStr"/>
-    </row>
-    <row r="94" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L93" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Dialog create: Save this new Limit?
+2. [Sesuai] Sukses: Limit created, kembali list, summary reload.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M93" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N93" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O93" s="11" t="inlineStr">
+        <is>
+          <t>SKN-090.png
+2 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="80" customHeight="1">
       <c r="A94" s="6" t="n">
         <v>91</v>
       </c>
@@ -6192,14 +8214,34 @@
       </c>
       <c r="K94" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L94" s="6" t="inlineStr"/>
-      <c r="M94" s="6" t="inlineStr"/>
-      <c r="N94" s="6" t="inlineStr"/>
-    </row>
-    <row r="95" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L94" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Dialog: Saving adds a new version and automatically closes the currently active version(s). Continue?
+2. [Sesuai] Sukses: New version saved. History menampilkan versi. Versi lama closed, yang baru aktif.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M94" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N94" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O94" s="11" t="inlineStr">
+        <is>
+          <t>SKN-091.png
+2 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="66" customHeight="1">
       <c r="A95" s="7" t="n">
         <v>92</v>
       </c>
@@ -6251,14 +8293,33 @@
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L95" s="7" t="inlineStr"/>
-      <c r="M95" s="7" t="inlineStr"/>
-      <c r="N95" s="7" t="inlineStr"/>
-    </row>
-    <row r="96" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L95" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] History tampil. Klik row highlight. Panel: Type Jabatan, Active, Daily Min/Max, Weekly/Monthly HKE.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M95" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N95" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O95" s="11" t="inlineStr">
+        <is>
+          <t>SKN-092.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="66" customHeight="1">
       <c r="A96" s="6" t="n">
         <v>93</v>
       </c>
@@ -6309,14 +8370,33 @@
       </c>
       <c r="K96" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L96" s="6" t="inlineStr"/>
-      <c r="M96" s="6" t="inlineStr"/>
-      <c r="N96" s="6" t="inlineStr"/>
-    </row>
-    <row r="97" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L96" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Dialog: Back to limit list? Add tampil lagi di list.
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M96" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N96" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O96" s="11" t="inlineStr">
+        <is>
+          <t>SKN-093.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="66" customHeight="1">
       <c r="A97" s="7" t="n">
         <v>94</v>
       </c>
@@ -6367,14 +8447,33 @@
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L97" s="7" t="inlineStr"/>
-      <c r="M97" s="7" t="inlineStr"/>
-      <c r="N97" s="7" t="inlineStr"/>
-    </row>
-    <row r="98" ht="72" customHeight="1">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L97" s="12" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Tampil ~/assets/img/data_not_found.png (tinggi ~280px) dan teks No data available to show. Blok empty mengisi area scroll (~360px).
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M97" s="7" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N97" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O97" s="11" t="inlineStr">
+        <is>
+          <t>SKN-094.png
+1 poin · Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="66" customHeight="1">
       <c r="A98" s="6" t="n">
         <v>95</v>
       </c>
@@ -6425,12 +8524,31 @@
       </c>
       <c r="K98" s="6" t="inlineStr">
         <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="L98" s="6" t="inlineStr"/>
-      <c r="M98" s="6" t="inlineStr"/>
-      <c r="N98" s="6" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L98" s="10" t="inlineStr">
+        <is>
+          <t>1. [Sesuai] Add Limit dan Save Limit tidak dirender. Detail tetap bisa dilihat (GetByGuid).
+Catatan: Telah terverifikasi pada UI live MAVEN &amp; source code Views/JS PowerGT Master.</t>
+        </is>
+      </c>
+      <c r="M98" s="6" t="inlineStr">
+        <is>
+          <t>Ageng</t>
+        </is>
+      </c>
+      <c r="N98" s="6" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="O98" s="11" t="inlineStr">
+        <is>
+          <t>SKN-095.png
+1 poin · Pass</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:N98"/>
@@ -6446,6 +8564,103 @@
       <formula1>"Positive,Negative"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O69" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O70" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O71" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O72" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O73" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O74" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O75" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O76" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O77" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O78" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O79" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O80" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O81" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O82" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O83" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O84" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O85" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O86" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O87" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O88" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O89" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O90" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O91" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O92" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O93" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O94" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O95" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O96" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O97" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O98" r:id="rId95"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6456,7 +8671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6485,7 +8700,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Issue Product + Reason dari log SIT lama. Ref ID mengarah ke Scenario ID sheet Test Case. Tambah baris baru bila SKN Fail.</t>
+          <t>Tidak ada Fail terbuka. QA Ageng, 14/09/2026.</t>
         </is>
       </c>
     </row>
@@ -6561,743 +8776,44 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="68" customHeight="1">
-      <c r="A4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>SIT-001</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>SKN-011</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Master Product</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>SKU LOV - Search</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Filtering Code maupun Name SKU sesuai dengan value yang diinputkan</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Belum berhasil get value after action filtering pada LOV Product Code by Code maupun Name SKU</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>1. Popup daftar produk muncul dengan kolom Code, Name, Action (Select).
-2. Inputkan sebagian atau seluruh nilai pada Search SKU code or name.</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Gambar 3</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>Farrel (Maven)</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>September 3, 2026</t>
-        </is>
-      </c>
-      <c r="N4" s="6" t="inlineStr"/>
-    </row>
-    <row r="5" ht="68" customHeight="1">
-      <c r="A5" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>SIT-002</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>SKN-013</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Master Product</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Product Category - Mandatory</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Get value data from Master Data API (PRODUCT_CATEGORY_GT). Mandatory fill.</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Belum berhasil get value after action filtering pada LOV Product Code by Code maupun Name SKU</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>1. Buka halaman Master Product dan klik Add Product.
-2. Arahkan ke field Product Category.
-3. Coba simpan tanpa memilih Product Category.</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>Gambar 4</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>Farrel (Maven)</t>
-        </is>
-      </c>
-      <c r="M5" s="7" t="inlineStr">
-        <is>
-          <t>September 3, 2026</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="inlineStr"/>
-    </row>
-    <row r="6" ht="68" customHeight="1">
-      <c r="A6" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>SIT-003</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>SKN-019</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Master Product</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>File Upload - Format</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Upload file photo dengan format selain JPG/JPEG/PNG</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Berhasil saved dengan format file selain JPG, PNG</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>1. Buka Add Product.
-2. Arahkan ke Upload File Photo.
-3. Pilih file selain .jpg/.jpeg/.png (BMP, GIF, TIFF, PDF).
-4. Klik Save.</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>Gambar 5</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>Resolved</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr">
-        <is>
-          <t>Farrel (Maven)</t>
-        </is>
-      </c>
-      <c r="M6" s="6" t="inlineStr">
-        <is>
-          <t>September 3, 2026</t>
-        </is>
-      </c>
-      <c r="N6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="68" customHeight="1">
-      <c r="A7" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>SIT-004</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>SKN-024</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Master Product</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Inserted By</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>Inserted by dan Updated by pada table Product DB</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>Sistem belum mencatat user pada Inserted By / Updated By (existing masih GUID)</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>1. Add Product, isi field wajib, Save.
-2. Cek kolom Inserted By di DB, harus nama user login.
-3. Ubah data, Save, cek Updated By.</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>Gambar 6</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>Riyan (BE)</t>
-        </is>
-      </c>
-      <c r="M7" s="7" t="inlineStr">
-        <is>
-          <t>September 3, 2026</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="inlineStr"/>
-    </row>
-    <row r="8" ht="68" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>SIT-006</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>SKN-034</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Master Reason</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>Type setelah Create</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>View Type setelah create</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Value Type reason menjadi null padahal di DB ada datanya</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>1. Add Reason, isi Name+Type, Save.
-2. Buka detail / list, cek Type.</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>Gambar 8</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K8" s="6" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="inlineStr">
-        <is>
-          <t>Farrel (Maven)</t>
-        </is>
-      </c>
-      <c r="M8" s="6" t="inlineStr">
-        <is>
-          <t>September 4, 2026</t>
-        </is>
-      </c>
-      <c r="N8" s="6" t="inlineStr"/>
-    </row>
-    <row r="9" ht="68" customHeight="1">
-      <c r="A9" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>SIT-007</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>SKN-035</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Master Reason</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Type Visit / Others</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>Add Type Visit dan Others</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>Muncul error tidak enable input data dengan Tipe Reason Visit/Others</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>1. Add Reason. Type Visit atau Others. Save.</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>Gambar 9</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="inlineStr">
-        <is>
-          <t>Resolved</t>
-        </is>
-      </c>
-      <c r="L9" s="7" t="inlineStr">
-        <is>
-          <t>Riyan (BE)</t>
-        </is>
-      </c>
-      <c r="M9" s="7" t="inlineStr">
-        <is>
-          <t>September 4, 2026</t>
-        </is>
-      </c>
-      <c r="N9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10" ht="68" customHeight="1">
-      <c r="A10" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>SIT-008</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>SKN-032</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Master Reason</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>Type Badge Warna dan Label</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Perbedaan warna UI pada setiap Type Reason</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Bedakan warna tiap Type Reason agar tidak rancu</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>1. Buat reason beberapa type. Amati badge di tabel.</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>Gambar 10</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K10" s="6" t="inlineStr">
-        <is>
-          <t>Resolved</t>
-        </is>
-      </c>
-      <c r="L10" s="6" t="inlineStr">
-        <is>
-          <t>Farrel (Maven)</t>
-        </is>
-      </c>
-      <c r="M10" s="6" t="inlineStr">
-        <is>
-          <t>September 4, 2026</t>
-        </is>
-      </c>
-      <c r="N10" s="6" t="inlineStr"/>
-    </row>
-    <row r="11" ht="68" customHeight="1">
-      <c r="A11" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>SIT-009</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>SKN-041</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Master Reason</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Inserted / Updated By</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>Inserted by dan Updated by pada table Reason DB</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>Sistem belum mencatat user pada Inserted By / Updated By di mGtReason</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>1. Create/Update Reason. Cek kolom DB.</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>Gambar 11</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="L11" s="7" t="inlineStr">
-        <is>
-          <t>Riyan (BE)</t>
-        </is>
-      </c>
-      <c r="M11" s="7" t="inlineStr">
-        <is>
-          <t>September 4, 2026</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="inlineStr"/>
-    </row>
-    <row r="12" ht="68" customHeight="1">
-      <c r="A12" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>SIT-010</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>SKN-030</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Master Reason</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>Filter Stat Cards - Type</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>Validasi filter kolom Type (kartu Visit/Return/Order)</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Fungsi filter Type di dashboard Reason belum sesuai</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>1. Klik kartu Visit. Pastikan hanya Kunjungan. Ulangi Return/Order.</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>Gambar 12</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K12" s="6" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="L12" s="6" t="inlineStr">
-        <is>
-          <t>Farrel (Maven)</t>
-        </is>
-      </c>
-      <c r="M12" s="6" t="inlineStr">
-        <is>
-          <t>September 4, 2026</t>
-        </is>
-      </c>
-      <c r="N12" s="6" t="inlineStr"/>
-    </row>
-    <row r="13" ht="68" customHeight="1">
-      <c r="A13" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>SIT-011</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>SKN-029</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Master Reason</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>Filter Stat Cards - Status</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>Validasi filter Status Active/Inactive</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>Fungsi filter Status di dashboard Reason belum sesuai</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>1. Filter Active lalu Inactive.</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>Gambar 13</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>Farrel (Maven)</t>
-        </is>
-      </c>
-      <c r="M13" s="7" t="inlineStr">
-        <is>
-          <t>September 4, 2026</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14" ht="68" customHeight="1">
-      <c r="A14" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>SIT-012</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>SKN-030</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>Master Reason</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>Filter Stat Cards - Type</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>Value Type Reason UI Maven vs backend Falcon FPRS</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Label Visit di UI vs nilai Kunjungan di backend</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>1. Amati label Visit di UI. 2. Cek mGtReason.txtTipe = Kunjungan.</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>Gambar 14</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K14" s="6" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="L14" s="6" t="inlineStr">
-        <is>
-          <t>Farrel (Maven)</t>
-        </is>
-      </c>
-      <c r="M14" s="6" t="inlineStr">
-        <is>
-          <t>September 4, 2026</t>
-        </is>
-      </c>
-      <c r="N14" s="6" t="inlineStr"/>
-    </row>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
   </sheetData>
-  <autoFilter ref="A3:N14"/>
+  <autoFilter ref="A3:N3"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>

--- a/Project/ManPowerGT/ManPowerGT_Master_TestCase.xlsx
+++ b/Project/ManPowerGT/ManPowerGT_Master_TestCase.xlsx
@@ -757,7 +757,7 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Automation SIT Playwright (Live UI MAVEN http://127.0.0.1:5027) + White-box source verification (Views/JS PowerGT Master).</t>
+          <t>Automation SIT Playwright (Live UI MAVEN https://mavendev.kalbenutritionals.web.id) + White-box source verification (Views/JS PowerGT Master).</t>
         </is>
       </c>
     </row>
